--- a/doc/рассчет/Таблица сопоставления названий.xlsx
+++ b/doc/рассчет/Таблица сопоставления названий.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KOTT\Documents\Учеба\System Design\GIT\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA9157F6-5070-4156-884D-2B9C42A422CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D001B7-9640-4904-A3F1-78636EB7F388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BE932E5D-0253-4FE7-9955-D860F268748E}"/>
   </bookViews>
@@ -858,14 +858,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBFA297-6AA4-480F-888C-F007D6616A8A}">
   <dimension ref="A1:C68"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="49.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>122</v>
       </c>
@@ -876,7 +876,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>119</v>
       </c>
@@ -887,7 +887,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>114</v>
       </c>
@@ -898,7 +898,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>116</v>
       </c>
@@ -909,7 +909,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>114</v>
       </c>
@@ -920,7 +920,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>112</v>
       </c>
@@ -931,7 +931,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>109</v>
       </c>
@@ -942,7 +942,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>107</v>
       </c>
@@ -953,7 +953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>104</v>
       </c>
@@ -964,7 +964,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>105</v>
       </c>
@@ -975,7 +975,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>103</v>
       </c>
@@ -986,7 +986,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>101</v>
       </c>
@@ -997,7 +997,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>99</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>97</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>95</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>93</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>91</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>89</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>87</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>85</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>83</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>81</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>79</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>77</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>75</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>73</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>35</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>71</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>68</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>66</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>64</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>62</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>60</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>58</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>56</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>54</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>52</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>50</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>48</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>46</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>44</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>42</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>39</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>37</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>35</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>33</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>30</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>28</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>26</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>24</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>22</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>19</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>17</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>15</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>13</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>11</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>9</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>7</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>4</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>2</v>
       </c>
@@ -1525,28 +1525,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B62"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B63"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B64"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B65"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B66"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B67"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2"/>
     </row>
   </sheetData>
